--- a/Data/EXCEL/Transfer/salemon/202208/2633-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/2633-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{743A5BDD-29EA-4678-89D5-94D5F6C0C658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B306DC-C545-4995-B3E1-B55239981856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="2633-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -72,12 +72,15 @@
   <si>
     <t>年增</t>
   </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -243,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -260,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -268,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -815,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -824,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -842,22 +853,22 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,17 +1226,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q240"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.875" customWidth="1"/>
-    <col min="2" max="5" width="9.875" customWidth="1"/>
-    <col min="6" max="6" width="9.5" customWidth="1"/>
-    <col min="7" max="7" width="10.875" customWidth="1"/>
-    <col min="8" max="11" width="9.875" customWidth="1"/>
-    <col min="12" max="12" width="9.5" customWidth="1"/>
-    <col min="13" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="2" max="5" width="14.125" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="15.375" customWidth="1"/>
+    <col min="8" max="17" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -4501,6 +4509,9387 @@
       </c>
       <c r="Q63" s="10">
         <v>6.91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>42979</v>
+      </c>
+      <c r="B64" s="7">
+        <v>26.6</v>
+      </c>
+      <c r="C64" s="7">
+        <v>24.1</v>
+      </c>
+      <c r="D64" s="7">
+        <v>26.6</v>
+      </c>
+      <c r="E64" s="7">
+        <v>23.55</v>
+      </c>
+      <c r="F64" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G64" s="8">
+        <v>-9.4</v>
+      </c>
+      <c r="H64" s="9">
+        <v>33.24</v>
+      </c>
+      <c r="I64" s="8">
+        <v>-11.1</v>
+      </c>
+      <c r="J64" s="10">
+        <v>3.85</v>
+      </c>
+      <c r="K64" s="9">
+        <v>320.3</v>
+      </c>
+      <c r="L64" s="10">
+        <v>6.53</v>
+      </c>
+      <c r="M64" s="9">
+        <v>33.24</v>
+      </c>
+      <c r="N64" s="8">
+        <v>-11.1</v>
+      </c>
+      <c r="O64" s="10">
+        <v>3.85</v>
+      </c>
+      <c r="P64" s="9">
+        <v>320.3</v>
+      </c>
+      <c r="Q64" s="10">
+        <v>6.53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>42948</v>
+      </c>
+      <c r="B65" s="7">
+        <v>25.4</v>
+      </c>
+      <c r="C65" s="7">
+        <v>26.6</v>
+      </c>
+      <c r="D65" s="7">
+        <v>26.85</v>
+      </c>
+      <c r="E65" s="7">
+        <v>24.6</v>
+      </c>
+      <c r="F65" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G65" s="10">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="H65" s="9">
+        <v>37.4</v>
+      </c>
+      <c r="I65" s="10">
+        <v>5.35</v>
+      </c>
+      <c r="J65" s="10">
+        <v>9.64</v>
+      </c>
+      <c r="K65" s="9">
+        <v>287</v>
+      </c>
+      <c r="L65" s="10">
+        <v>6.85</v>
+      </c>
+      <c r="M65" s="9">
+        <v>37.4</v>
+      </c>
+      <c r="N65" s="10">
+        <v>5.35</v>
+      </c>
+      <c r="O65" s="10">
+        <v>9.64</v>
+      </c>
+      <c r="P65" s="9">
+        <v>287</v>
+      </c>
+      <c r="Q65" s="10">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>42917</v>
+      </c>
+      <c r="B66" s="7">
+        <v>25.5</v>
+      </c>
+      <c r="C66" s="7">
+        <v>26.05</v>
+      </c>
+      <c r="D66" s="7">
+        <v>26.25</v>
+      </c>
+      <c r="E66" s="7">
+        <v>25</v>
+      </c>
+      <c r="F66" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="G66" s="10">
+        <v>2.36</v>
+      </c>
+      <c r="H66" s="9">
+        <v>35.5</v>
+      </c>
+      <c r="I66" s="10">
+        <v>8.68</v>
+      </c>
+      <c r="J66" s="10">
+        <v>4.26</v>
+      </c>
+      <c r="K66" s="9">
+        <v>249.6</v>
+      </c>
+      <c r="L66" s="10">
+        <v>6.44</v>
+      </c>
+      <c r="M66" s="9">
+        <v>35.5</v>
+      </c>
+      <c r="N66" s="10">
+        <v>8.68</v>
+      </c>
+      <c r="O66" s="10">
+        <v>4.26</v>
+      </c>
+      <c r="P66" s="9">
+        <v>249.6</v>
+      </c>
+      <c r="Q66" s="10">
+        <v>6.44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>42887</v>
+      </c>
+      <c r="B67" s="7">
+        <v>25.2</v>
+      </c>
+      <c r="C67" s="7">
+        <v>25.45</v>
+      </c>
+      <c r="D67" s="7">
+        <v>27.5</v>
+      </c>
+      <c r="E67" s="7">
+        <v>25.1</v>
+      </c>
+      <c r="F67" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G67" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="H67" s="9">
+        <v>32.67</v>
+      </c>
+      <c r="I67" s="8">
+        <v>-11.9</v>
+      </c>
+      <c r="J67" s="8">
+        <v>-2.09</v>
+      </c>
+      <c r="K67" s="9">
+        <v>214.1</v>
+      </c>
+      <c r="L67" s="10">
+        <v>6.81</v>
+      </c>
+      <c r="M67" s="9">
+        <v>32.67</v>
+      </c>
+      <c r="N67" s="8">
+        <v>-11.9</v>
+      </c>
+      <c r="O67" s="8">
+        <v>-2.09</v>
+      </c>
+      <c r="P67" s="9">
+        <v>214.1</v>
+      </c>
+      <c r="Q67" s="10">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>42856</v>
+      </c>
+      <c r="B68" s="7">
+        <v>23.4</v>
+      </c>
+      <c r="C68" s="7">
+        <v>25.4</v>
+      </c>
+      <c r="D68" s="7">
+        <v>25.4</v>
+      </c>
+      <c r="E68" s="7">
+        <v>22.7</v>
+      </c>
+      <c r="F68" s="10">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G68" s="10">
+        <v>8.7799999999999994</v>
+      </c>
+      <c r="H68" s="9">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="I68" s="10">
+        <v>2.14</v>
+      </c>
+      <c r="J68" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="K68" s="9">
+        <v>181.5</v>
+      </c>
+      <c r="L68" s="10">
+        <v>8.59</v>
+      </c>
+      <c r="M68" s="9">
+        <v>37.090000000000003</v>
+      </c>
+      <c r="N68" s="10">
+        <v>2.14</v>
+      </c>
+      <c r="O68" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="P68" s="9">
+        <v>181.5</v>
+      </c>
+      <c r="Q68" s="10">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>42826</v>
+      </c>
+      <c r="B69" s="7">
+        <v>21.5</v>
+      </c>
+      <c r="C69" s="7">
+        <v>23.35</v>
+      </c>
+      <c r="D69" s="7">
+        <v>23.5</v>
+      </c>
+      <c r="E69" s="7">
+        <v>21.25</v>
+      </c>
+      <c r="F69" s="10">
+        <v>2</v>
+      </c>
+      <c r="G69" s="10">
+        <v>9.3699999999999992</v>
+      </c>
+      <c r="H69" s="9">
+        <v>36.31</v>
+      </c>
+      <c r="I69" s="10">
+        <v>2.16</v>
+      </c>
+      <c r="J69" s="10">
+        <v>6.91</v>
+      </c>
+      <c r="K69" s="9">
+        <v>144.4</v>
+      </c>
+      <c r="L69" s="10">
+        <v>7.89</v>
+      </c>
+      <c r="M69" s="9">
+        <v>36.31</v>
+      </c>
+      <c r="N69" s="10">
+        <v>2.16</v>
+      </c>
+      <c r="O69" s="10">
+        <v>6.91</v>
+      </c>
+      <c r="P69" s="9">
+        <v>144.4</v>
+      </c>
+      <c r="Q69" s="10">
+        <v>7.89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>42795</v>
+      </c>
+      <c r="B70" s="7">
+        <v>21.6</v>
+      </c>
+      <c r="C70" s="7">
+        <v>21.35</v>
+      </c>
+      <c r="D70" s="7">
+        <v>21.7</v>
+      </c>
+      <c r="E70" s="7">
+        <v>20.6</v>
+      </c>
+      <c r="F70" s="8">
+        <v>-0.2</v>
+      </c>
+      <c r="G70" s="8">
+        <v>-0.93</v>
+      </c>
+      <c r="H70" s="9">
+        <v>35.54</v>
+      </c>
+      <c r="I70" s="10">
+        <v>5.37</v>
+      </c>
+      <c r="J70" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="K70" s="9">
+        <v>108.1</v>
+      </c>
+      <c r="L70" s="10">
+        <v>8.23</v>
+      </c>
+      <c r="M70" s="9">
+        <v>35.54</v>
+      </c>
+      <c r="N70" s="10">
+        <v>5.37</v>
+      </c>
+      <c r="O70" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="P70" s="9">
+        <v>108.1</v>
+      </c>
+      <c r="Q70" s="10">
+        <v>8.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>42767</v>
+      </c>
+      <c r="B71" s="7">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="C71" s="7">
+        <v>21.55</v>
+      </c>
+      <c r="D71" s="7">
+        <v>21.85</v>
+      </c>
+      <c r="E71" s="7">
+        <v>19</v>
+      </c>
+      <c r="F71" s="10">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="G71" s="10">
+        <v>12.83</v>
+      </c>
+      <c r="H71" s="9">
+        <v>33.729999999999997</v>
+      </c>
+      <c r="I71" s="8">
+        <v>-13</v>
+      </c>
+      <c r="J71" s="8">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="K71" s="9">
+        <v>72.510000000000005</v>
+      </c>
+      <c r="L71" s="10">
+        <v>6.62</v>
+      </c>
+      <c r="M71" s="9">
+        <v>33.729999999999997</v>
+      </c>
+      <c r="N71" s="8">
+        <v>-13</v>
+      </c>
+      <c r="O71" s="8">
+        <v>-2.5499999999999998</v>
+      </c>
+      <c r="P71" s="9">
+        <v>72.510000000000005</v>
+      </c>
+      <c r="Q71" s="10">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>42736</v>
+      </c>
+      <c r="B72" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C72" s="7">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D72" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="E72" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="F72" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="G72" s="10">
+        <v>3.8</v>
+      </c>
+      <c r="H72" s="9">
+        <v>38.78</v>
+      </c>
+      <c r="I72" s="10">
+        <v>6.16</v>
+      </c>
+      <c r="J72" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="K72" s="9">
+        <v>38.78</v>
+      </c>
+      <c r="L72" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="M72" s="9">
+        <v>38.78</v>
+      </c>
+      <c r="N72" s="10">
+        <v>6.16</v>
+      </c>
+      <c r="O72" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="P72" s="9">
+        <v>38.78</v>
+      </c>
+      <c r="Q72" s="10">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>42705</v>
+      </c>
+      <c r="B73" s="7">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="C73" s="7">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D73" s="7">
+        <v>19.2</v>
+      </c>
+      <c r="E73" s="7">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="F73" s="8">
+        <v>-0.65</v>
+      </c>
+      <c r="G73" s="8">
+        <v>-3.41</v>
+      </c>
+      <c r="H73" s="9">
+        <v>36.520000000000003</v>
+      </c>
+      <c r="I73" s="10">
+        <v>8.81</v>
+      </c>
+      <c r="J73" s="10">
+        <v>8.65</v>
+      </c>
+      <c r="K73" s="9">
+        <v>406.1</v>
+      </c>
+      <c r="L73" s="8">
+        <v>-21.8</v>
+      </c>
+      <c r="M73" s="9">
+        <v>36.520000000000003</v>
+      </c>
+      <c r="N73" s="10">
+        <v>8.81</v>
+      </c>
+      <c r="O73" s="10">
+        <v>8.65</v>
+      </c>
+      <c r="P73" s="9">
+        <v>406.1</v>
+      </c>
+      <c r="Q73" s="8">
+        <v>-21.8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>42675</v>
+      </c>
+      <c r="B74" s="7">
+        <v>20.8</v>
+      </c>
+      <c r="C74" s="7">
+        <v>19.05</v>
+      </c>
+      <c r="D74" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="E74" s="7">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="F74" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="G74" s="8">
+        <v>-8.6300000000000008</v>
+      </c>
+      <c r="H74" s="9">
+        <v>33.56</v>
+      </c>
+      <c r="I74" s="8">
+        <v>-5.18</v>
+      </c>
+      <c r="J74" s="10">
+        <v>2.17</v>
+      </c>
+      <c r="K74" s="9">
+        <v>369.6</v>
+      </c>
+      <c r="L74" s="8">
+        <v>-23.8</v>
+      </c>
+      <c r="M74" s="9">
+        <v>33.56</v>
+      </c>
+      <c r="N74" s="8">
+        <v>-5.18</v>
+      </c>
+      <c r="O74" s="10">
+        <v>2.17</v>
+      </c>
+      <c r="P74" s="9">
+        <v>369.6</v>
+      </c>
+      <c r="Q74" s="8">
+        <v>-23.8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>42644</v>
+      </c>
+      <c r="B75" s="7">
+        <v>20.6</v>
+      </c>
+      <c r="C75" s="7">
+        <v>20.85</v>
+      </c>
+      <c r="D75" s="7">
+        <v>24.8</v>
+      </c>
+      <c r="E75" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="F75" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="G75" s="10">
+        <v>37.619999999999997</v>
+      </c>
+      <c r="H75" s="9">
+        <v>35.4</v>
+      </c>
+      <c r="I75" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="J75" s="8">
+        <v>-77</v>
+      </c>
+      <c r="K75" s="9">
+        <v>336</v>
+      </c>
+      <c r="L75" s="8">
+        <v>-25.7</v>
+      </c>
+      <c r="M75" s="9">
+        <v>35.4</v>
+      </c>
+      <c r="N75" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="O75" s="8">
+        <v>-77</v>
+      </c>
+      <c r="P75" s="9">
+        <v>336</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>-25.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>42614</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="9">
+        <v>32</v>
+      </c>
+      <c r="I76" s="8">
+        <v>-6.19</v>
+      </c>
+      <c r="J76" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="K76" s="9">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="L76" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="M76" s="9">
+        <v>32</v>
+      </c>
+      <c r="N76" s="8">
+        <v>-6.19</v>
+      </c>
+      <c r="O76" s="8">
+        <v>-1.05</v>
+      </c>
+      <c r="P76" s="9">
+        <v>300.60000000000002</v>
+      </c>
+      <c r="Q76" s="10">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>42583</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H77" s="9">
+        <v>34.11</v>
+      </c>
+      <c r="I77" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="J77" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="K77" s="9">
+        <v>268.60000000000002</v>
+      </c>
+      <c r="L77" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="M77" s="9">
+        <v>34.11</v>
+      </c>
+      <c r="N77" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="O77" s="10">
+        <v>2.7</v>
+      </c>
+      <c r="P77" s="9">
+        <v>268.60000000000002</v>
+      </c>
+      <c r="Q77" s="10">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>42552</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H78" s="9">
+        <v>34.049999999999997</v>
+      </c>
+      <c r="I78" s="10">
+        <v>2.04</v>
+      </c>
+      <c r="J78" s="10">
+        <v>1.72</v>
+      </c>
+      <c r="K78" s="9">
+        <v>234.5</v>
+      </c>
+      <c r="L78" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="M78" s="9">
+        <v>34.049999999999997</v>
+      </c>
+      <c r="N78" s="10">
+        <v>2.04</v>
+      </c>
+      <c r="O78" s="10">
+        <v>1.72</v>
+      </c>
+      <c r="P78" s="9">
+        <v>234.5</v>
+      </c>
+      <c r="Q78" s="10">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>42522</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="9">
+        <v>33.36</v>
+      </c>
+      <c r="I79" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="J79" s="10">
+        <v>1.84</v>
+      </c>
+      <c r="K79" s="9">
+        <v>200.5</v>
+      </c>
+      <c r="L79" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="M79" s="9">
+        <v>33.36</v>
+      </c>
+      <c r="N79" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="O79" s="10">
+        <v>1.84</v>
+      </c>
+      <c r="P79" s="9">
+        <v>200.5</v>
+      </c>
+      <c r="Q79" s="10">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>42491</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H80" s="9">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="I80" s="8">
+        <v>-1.96</v>
+      </c>
+      <c r="J80" s="8">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="K80" s="9">
+        <v>167.1</v>
+      </c>
+      <c r="L80" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M80" s="9">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="N80" s="8">
+        <v>-1.96</v>
+      </c>
+      <c r="O80" s="8">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="P80" s="9">
+        <v>167.1</v>
+      </c>
+      <c r="Q80" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>42461</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="9">
+        <v>33.97</v>
+      </c>
+      <c r="I81" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="J81" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="K81" s="9">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="L81" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="M81" s="9">
+        <v>33.97</v>
+      </c>
+      <c r="N81" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="O81" s="10">
+        <v>0.88</v>
+      </c>
+      <c r="P81" s="9">
+        <v>133.80000000000001</v>
+      </c>
+      <c r="Q81" s="10">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>42430</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H82" s="9">
+        <v>31.83</v>
+      </c>
+      <c r="I82" s="8">
+        <v>-8.0399999999999991</v>
+      </c>
+      <c r="J82" s="8">
+        <v>-3.43</v>
+      </c>
+      <c r="K82" s="9">
+        <v>99.83</v>
+      </c>
+      <c r="L82" s="10">
+        <v>0.54</v>
+      </c>
+      <c r="M82" s="9">
+        <v>31.83</v>
+      </c>
+      <c r="N82" s="8">
+        <v>-8.0399999999999991</v>
+      </c>
+      <c r="O82" s="8">
+        <v>-3.43</v>
+      </c>
+      <c r="P82" s="9">
+        <v>99.83</v>
+      </c>
+      <c r="Q82" s="10">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>42401</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H83" s="9">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="I83" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="J83" s="8">
+        <v>-0.41</v>
+      </c>
+      <c r="K83" s="9">
+        <v>68</v>
+      </c>
+      <c r="L83" s="10">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="M83" s="9">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="N83" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="O83" s="8">
+        <v>-0.41</v>
+      </c>
+      <c r="P83" s="9">
+        <v>68</v>
+      </c>
+      <c r="Q83" s="10">
+        <v>2.5299999999999998</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>42370</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="9">
+        <v>33.380000000000003</v>
+      </c>
+      <c r="I84" s="8">
+        <v>-0.68</v>
+      </c>
+      <c r="J84" s="10">
+        <v>5.77</v>
+      </c>
+      <c r="K84" s="9">
+        <v>33.380000000000003</v>
+      </c>
+      <c r="L84" s="10">
+        <v>5.77</v>
+      </c>
+      <c r="M84" s="9">
+        <v>33.380000000000003</v>
+      </c>
+      <c r="N84" s="8">
+        <v>-0.68</v>
+      </c>
+      <c r="O84" s="10">
+        <v>5.77</v>
+      </c>
+      <c r="P84" s="9">
+        <v>33.380000000000003</v>
+      </c>
+      <c r="Q84" s="10">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>42339</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H85" s="9">
+        <v>33.61</v>
+      </c>
+      <c r="I85" s="10">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="J85" s="10">
+        <v>3.64</v>
+      </c>
+      <c r="K85" s="9">
+        <v>519</v>
+      </c>
+      <c r="L85" s="10">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="M85" s="9">
+        <v>33.61</v>
+      </c>
+      <c r="N85" s="10">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="O85" s="10">
+        <v>3.64</v>
+      </c>
+      <c r="P85" s="9">
+        <v>519</v>
+      </c>
+      <c r="Q85" s="10">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>42309</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H86" s="9">
+        <v>32.85</v>
+      </c>
+      <c r="I86" s="8">
+        <v>-78.7</v>
+      </c>
+      <c r="J86" s="10">
+        <v>3.12</v>
+      </c>
+      <c r="K86" s="9">
+        <v>485.4</v>
+      </c>
+      <c r="L86" s="10">
+        <v>37.6</v>
+      </c>
+      <c r="M86" s="9">
+        <v>32.85</v>
+      </c>
+      <c r="N86" s="8">
+        <v>-78.7</v>
+      </c>
+      <c r="O86" s="10">
+        <v>3.12</v>
+      </c>
+      <c r="P86" s="9">
+        <v>485.4</v>
+      </c>
+      <c r="Q86" s="10">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>42278</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H87" s="9">
+        <v>154.1</v>
+      </c>
+      <c r="I87" s="10">
+        <v>376.6</v>
+      </c>
+      <c r="J87" s="10">
+        <v>366.5</v>
+      </c>
+      <c r="K87" s="9">
+        <v>452.6</v>
+      </c>
+      <c r="L87" s="10">
+        <v>41.1</v>
+      </c>
+      <c r="M87" s="9">
+        <v>154.1</v>
+      </c>
+      <c r="N87" s="10">
+        <v>376.6</v>
+      </c>
+      <c r="O87" s="10">
+        <v>366.5</v>
+      </c>
+      <c r="P87" s="9">
+        <v>452.6</v>
+      </c>
+      <c r="Q87" s="10">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>42248</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="9">
+        <v>32.340000000000003</v>
+      </c>
+      <c r="I88" s="8">
+        <v>-2.62</v>
+      </c>
+      <c r="J88" s="10">
+        <v>2.99</v>
+      </c>
+      <c r="K88" s="9">
+        <v>298.39999999999998</v>
+      </c>
+      <c r="L88" s="10">
+        <v>3.7</v>
+      </c>
+      <c r="M88" s="9">
+        <v>32.340000000000003</v>
+      </c>
+      <c r="N88" s="8">
+        <v>-2.62</v>
+      </c>
+      <c r="O88" s="10">
+        <v>2.99</v>
+      </c>
+      <c r="P88" s="9">
+        <v>298.39999999999998</v>
+      </c>
+      <c r="Q88" s="10">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>42217</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H89" s="9">
+        <v>33.21</v>
+      </c>
+      <c r="I89" s="8">
+        <v>-0.76</v>
+      </c>
+      <c r="J89" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="K89" s="9">
+        <v>266.10000000000002</v>
+      </c>
+      <c r="L89" s="10">
+        <v>3.78</v>
+      </c>
+      <c r="M89" s="9">
+        <v>33.21</v>
+      </c>
+      <c r="N89" s="8">
+        <v>-0.76</v>
+      </c>
+      <c r="O89" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="P89" s="9">
+        <v>266.10000000000002</v>
+      </c>
+      <c r="Q89" s="10">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>42186</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H90" s="9">
+        <v>33.47</v>
+      </c>
+      <c r="I90" s="10">
+        <v>2.16</v>
+      </c>
+      <c r="J90" s="10">
+        <v>3.07</v>
+      </c>
+      <c r="K90" s="9">
+        <v>232.9</v>
+      </c>
+      <c r="L90" s="10">
+        <v>4.12</v>
+      </c>
+      <c r="M90" s="9">
+        <v>33.47</v>
+      </c>
+      <c r="N90" s="10">
+        <v>2.16</v>
+      </c>
+      <c r="O90" s="10">
+        <v>3.07</v>
+      </c>
+      <c r="P90" s="9">
+        <v>232.9</v>
+      </c>
+      <c r="Q90" s="10">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>42156</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H91" s="9">
+        <v>32.76</v>
+      </c>
+      <c r="I91" s="8">
+        <v>-2.7</v>
+      </c>
+      <c r="J91" s="10">
+        <v>4.04</v>
+      </c>
+      <c r="K91" s="9">
+        <v>199.4</v>
+      </c>
+      <c r="L91" s="10">
+        <v>4.29</v>
+      </c>
+      <c r="M91" s="9">
+        <v>32.76</v>
+      </c>
+      <c r="N91" s="8">
+        <v>-2.7</v>
+      </c>
+      <c r="O91" s="10">
+        <v>4.04</v>
+      </c>
+      <c r="P91" s="9">
+        <v>199.4</v>
+      </c>
+      <c r="Q91" s="10">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>42125</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H92" s="9">
+        <v>33.67</v>
+      </c>
+      <c r="I92" s="9">
+        <v>0</v>
+      </c>
+      <c r="J92" s="10">
+        <v>3.92</v>
+      </c>
+      <c r="K92" s="9">
+        <v>166.6</v>
+      </c>
+      <c r="L92" s="10">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="M92" s="9">
+        <v>33.67</v>
+      </c>
+      <c r="N92" s="9">
+        <v>0</v>
+      </c>
+      <c r="O92" s="10">
+        <v>3.92</v>
+      </c>
+      <c r="P92" s="9">
+        <v>166.6</v>
+      </c>
+      <c r="Q92" s="10">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>42095</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H93" s="9">
+        <v>33.67</v>
+      </c>
+      <c r="I93" s="10">
+        <v>2.13</v>
+      </c>
+      <c r="J93" s="10">
+        <v>4.71</v>
+      </c>
+      <c r="K93" s="9">
+        <v>133</v>
+      </c>
+      <c r="L93" s="10">
+        <v>4.45</v>
+      </c>
+      <c r="M93" s="9">
+        <v>33.67</v>
+      </c>
+      <c r="N93" s="10">
+        <v>2.13</v>
+      </c>
+      <c r="O93" s="10">
+        <v>4.71</v>
+      </c>
+      <c r="P93" s="9">
+        <v>133</v>
+      </c>
+      <c r="Q93" s="10">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>42064</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H94" s="9">
+        <v>32.96</v>
+      </c>
+      <c r="I94" s="8">
+        <v>-5.16</v>
+      </c>
+      <c r="J94" s="10">
+        <v>2.86</v>
+      </c>
+      <c r="K94" s="9">
+        <v>99.29</v>
+      </c>
+      <c r="L94" s="10">
+        <v>4.37</v>
+      </c>
+      <c r="M94" s="9">
+        <v>32.96</v>
+      </c>
+      <c r="N94" s="8">
+        <v>-5.16</v>
+      </c>
+      <c r="O94" s="10">
+        <v>2.86</v>
+      </c>
+      <c r="P94" s="9">
+        <v>99.29</v>
+      </c>
+      <c r="Q94" s="10">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>42036</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H95" s="9">
+        <v>34.76</v>
+      </c>
+      <c r="I95" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="J95" s="10">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="K95" s="9">
+        <v>66.319999999999993</v>
+      </c>
+      <c r="L95" s="10">
+        <v>5.13</v>
+      </c>
+      <c r="M95" s="9">
+        <v>34.76</v>
+      </c>
+      <c r="N95" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="O95" s="10">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="P95" s="9">
+        <v>66.319999999999993</v>
+      </c>
+      <c r="Q95" s="10">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>42005</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="9">
+        <v>31.56</v>
+      </c>
+      <c r="I96" s="8">
+        <v>-2.68</v>
+      </c>
+      <c r="J96" s="10">
+        <v>1.39</v>
+      </c>
+      <c r="K96" s="9">
+        <v>31.56</v>
+      </c>
+      <c r="L96" s="10">
+        <v>1.39</v>
+      </c>
+      <c r="M96" s="9">
+        <v>31.56</v>
+      </c>
+      <c r="N96" s="8">
+        <v>-2.68</v>
+      </c>
+      <c r="O96" s="10">
+        <v>1.39</v>
+      </c>
+      <c r="P96" s="9">
+        <v>31.56</v>
+      </c>
+      <c r="Q96" s="10">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>41974</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H97" s="9">
+        <v>32.43</v>
+      </c>
+      <c r="I97" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="J97" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="K97" s="9">
+        <v>385.1</v>
+      </c>
+      <c r="L97" s="10">
+        <v>6.66</v>
+      </c>
+      <c r="M97" s="9">
+        <v>32.43</v>
+      </c>
+      <c r="N97" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="O97" s="10">
+        <v>0.91</v>
+      </c>
+      <c r="P97" s="9">
+        <v>385.1</v>
+      </c>
+      <c r="Q97" s="10">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>41944</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H98" s="9">
+        <v>31.86</v>
+      </c>
+      <c r="I98" s="8">
+        <v>-3.58</v>
+      </c>
+      <c r="J98" s="10">
+        <v>3.26</v>
+      </c>
+      <c r="K98" s="9">
+        <v>352.7</v>
+      </c>
+      <c r="L98" s="10">
+        <v>7.23</v>
+      </c>
+      <c r="M98" s="9">
+        <v>31.86</v>
+      </c>
+      <c r="N98" s="8">
+        <v>-3.58</v>
+      </c>
+      <c r="O98" s="10">
+        <v>3.26</v>
+      </c>
+      <c r="P98" s="9">
+        <v>352.7</v>
+      </c>
+      <c r="Q98" s="10">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>41913</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H99" s="9">
+        <v>33.04</v>
+      </c>
+      <c r="I99" s="10">
+        <v>5.21</v>
+      </c>
+      <c r="J99" s="10">
+        <v>8.36</v>
+      </c>
+      <c r="K99" s="9">
+        <v>320.8</v>
+      </c>
+      <c r="L99" s="10">
+        <v>7.64</v>
+      </c>
+      <c r="M99" s="9">
+        <v>33.04</v>
+      </c>
+      <c r="N99" s="10">
+        <v>5.21</v>
+      </c>
+      <c r="O99" s="10">
+        <v>8.36</v>
+      </c>
+      <c r="P99" s="9">
+        <v>320.8</v>
+      </c>
+      <c r="Q99" s="10">
+        <v>7.64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>41883</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H100" s="9">
+        <v>31.4</v>
+      </c>
+      <c r="I100" s="8">
+        <v>-4.03</v>
+      </c>
+      <c r="J100" s="10">
+        <v>4.07</v>
+      </c>
+      <c r="K100" s="9">
+        <v>287.8</v>
+      </c>
+      <c r="L100" s="10">
+        <v>7.55</v>
+      </c>
+      <c r="M100" s="9">
+        <v>31.4</v>
+      </c>
+      <c r="N100" s="8">
+        <v>-4.03</v>
+      </c>
+      <c r="O100" s="10">
+        <v>4.07</v>
+      </c>
+      <c r="P100" s="9">
+        <v>287.8</v>
+      </c>
+      <c r="Q100" s="10">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>41852</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="9">
+        <v>32.72</v>
+      </c>
+      <c r="I101" s="10">
+        <v>0.77</v>
+      </c>
+      <c r="J101" s="10">
+        <v>6.52</v>
+      </c>
+      <c r="K101" s="9">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="L101" s="10">
+        <v>8</v>
+      </c>
+      <c r="M101" s="9">
+        <v>32.72</v>
+      </c>
+      <c r="N101" s="10">
+        <v>0.77</v>
+      </c>
+      <c r="O101" s="10">
+        <v>6.52</v>
+      </c>
+      <c r="P101" s="9">
+        <v>256.39999999999998</v>
+      </c>
+      <c r="Q101" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>41821</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H102" s="9">
+        <v>32.47</v>
+      </c>
+      <c r="I102" s="10">
+        <v>3.11</v>
+      </c>
+      <c r="J102" s="10">
+        <v>7.46</v>
+      </c>
+      <c r="K102" s="9">
+        <v>223.6</v>
+      </c>
+      <c r="L102" s="10">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="M102" s="9">
+        <v>32.47</v>
+      </c>
+      <c r="N102" s="10">
+        <v>3.11</v>
+      </c>
+      <c r="O102" s="10">
+        <v>7.46</v>
+      </c>
+      <c r="P102" s="9">
+        <v>223.6</v>
+      </c>
+      <c r="Q102" s="10">
+        <v>8.2200000000000006</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>41791</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103" s="9">
+        <v>31.49</v>
+      </c>
+      <c r="I103" s="8">
+        <v>-2.81</v>
+      </c>
+      <c r="J103" s="10">
+        <v>7.81</v>
+      </c>
+      <c r="K103" s="9">
+        <v>191.2</v>
+      </c>
+      <c r="L103" s="10">
+        <v>8.35</v>
+      </c>
+      <c r="M103" s="9">
+        <v>31.49</v>
+      </c>
+      <c r="N103" s="8">
+        <v>-2.81</v>
+      </c>
+      <c r="O103" s="10">
+        <v>7.81</v>
+      </c>
+      <c r="P103" s="9">
+        <v>191.2</v>
+      </c>
+      <c r="Q103" s="10">
+        <v>8.35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>41760</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H104" s="9">
+        <v>32.4</v>
+      </c>
+      <c r="I104" s="10">
+        <v>0.76</v>
+      </c>
+      <c r="J104" s="10">
+        <v>11</v>
+      </c>
+      <c r="K104" s="9">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="L104" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="M104" s="9">
+        <v>32.4</v>
+      </c>
+      <c r="N104" s="10">
+        <v>0.76</v>
+      </c>
+      <c r="O104" s="10">
+        <v>11</v>
+      </c>
+      <c r="P104" s="9">
+        <v>159.69999999999999</v>
+      </c>
+      <c r="Q104" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>41730</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H105" s="9">
+        <v>32.15</v>
+      </c>
+      <c r="I105" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="J105" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="K105" s="9">
+        <v>127.3</v>
+      </c>
+      <c r="L105" s="10">
+        <v>7.82</v>
+      </c>
+      <c r="M105" s="9">
+        <v>32.15</v>
+      </c>
+      <c r="N105" s="10">
+        <v>0.33</v>
+      </c>
+      <c r="O105" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="P105" s="9">
+        <v>127.3</v>
+      </c>
+      <c r="Q105" s="10">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>41699</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H106" s="9">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="I106" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J106" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K106" s="9">
+        <v>95.12</v>
+      </c>
+      <c r="L106" s="10">
+        <v>7.61</v>
+      </c>
+      <c r="M106" s="9">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="N106" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O106" s="10">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P106" s="9">
+        <v>95.12</v>
+      </c>
+      <c r="Q106" s="10">
+        <v>7.61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>41671</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H107" s="9">
+        <v>31.95</v>
+      </c>
+      <c r="I107" s="10">
+        <v>2.63</v>
+      </c>
+      <c r="J107" s="10">
+        <v>4.76</v>
+      </c>
+      <c r="K107" s="9">
+        <v>63.08</v>
+      </c>
+      <c r="L107" s="10">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="M107" s="9">
+        <v>31.95</v>
+      </c>
+      <c r="N107" s="10">
+        <v>2.63</v>
+      </c>
+      <c r="O107" s="10">
+        <v>4.76</v>
+      </c>
+      <c r="P107" s="9">
+        <v>63.08</v>
+      </c>
+      <c r="Q107" s="10">
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>41640</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H108" s="9">
+        <v>31.13</v>
+      </c>
+      <c r="I108" s="8">
+        <v>-3.13</v>
+      </c>
+      <c r="J108" s="10">
+        <v>13.8</v>
+      </c>
+      <c r="K108" s="9">
+        <v>31.13</v>
+      </c>
+      <c r="L108" s="10">
+        <v>13.8</v>
+      </c>
+      <c r="M108" s="9">
+        <v>31.13</v>
+      </c>
+      <c r="N108" s="8">
+        <v>-3.13</v>
+      </c>
+      <c r="O108" s="10">
+        <v>13.8</v>
+      </c>
+      <c r="P108" s="9">
+        <v>31.13</v>
+      </c>
+      <c r="Q108" s="10">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>41609</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H109" s="9">
+        <v>32.14</v>
+      </c>
+      <c r="I109" s="10">
+        <v>4.17</v>
+      </c>
+      <c r="J109" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="K109" s="9">
+        <v>361</v>
+      </c>
+      <c r="L109" s="10">
+        <v>6.22</v>
+      </c>
+      <c r="M109" s="9">
+        <v>32.14</v>
+      </c>
+      <c r="N109" s="10">
+        <v>4.17</v>
+      </c>
+      <c r="O109" s="10">
+        <v>5.7</v>
+      </c>
+      <c r="P109" s="9">
+        <v>361</v>
+      </c>
+      <c r="Q109" s="10">
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>41579</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H110" s="9">
+        <v>30.85</v>
+      </c>
+      <c r="I110" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="J110" s="10">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K110" s="9">
+        <v>328.9</v>
+      </c>
+      <c r="L110" s="10">
+        <v>6.27</v>
+      </c>
+      <c r="M110" s="9">
+        <v>30.85</v>
+      </c>
+      <c r="N110" s="10">
+        <v>1.17</v>
+      </c>
+      <c r="O110" s="10">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="P110" s="9">
+        <v>328.9</v>
+      </c>
+      <c r="Q110" s="10">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>41548</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H111" s="9">
+        <v>30.49</v>
+      </c>
+      <c r="I111" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="J111" s="10">
+        <v>5.53</v>
+      </c>
+      <c r="K111" s="9">
+        <v>298</v>
+      </c>
+      <c r="L111" s="10">
+        <v>6.02</v>
+      </c>
+      <c r="M111" s="9">
+        <v>30.49</v>
+      </c>
+      <c r="N111" s="10">
+        <v>1.05</v>
+      </c>
+      <c r="O111" s="10">
+        <v>5.53</v>
+      </c>
+      <c r="P111" s="9">
+        <v>298</v>
+      </c>
+      <c r="Q111" s="10">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>41518</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H112" s="9">
+        <v>30.17</v>
+      </c>
+      <c r="I112" s="8">
+        <v>-1.77</v>
+      </c>
+      <c r="J112" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="K112" s="9">
+        <v>267.5</v>
+      </c>
+      <c r="L112" s="10">
+        <v>6.07</v>
+      </c>
+      <c r="M112" s="9">
+        <v>30.17</v>
+      </c>
+      <c r="N112" s="8">
+        <v>-1.77</v>
+      </c>
+      <c r="O112" s="10">
+        <v>7.4</v>
+      </c>
+      <c r="P112" s="9">
+        <v>267.5</v>
+      </c>
+      <c r="Q112" s="10">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>41487</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H113" s="9">
+        <v>30.72</v>
+      </c>
+      <c r="I113" s="10">
+        <v>1.66</v>
+      </c>
+      <c r="J113" s="10">
+        <v>8.92</v>
+      </c>
+      <c r="K113" s="9">
+        <v>237.4</v>
+      </c>
+      <c r="L113" s="10">
+        <v>5.91</v>
+      </c>
+      <c r="M113" s="9">
+        <v>30.72</v>
+      </c>
+      <c r="N113" s="10">
+        <v>1.67</v>
+      </c>
+      <c r="O113" s="10">
+        <v>8.92</v>
+      </c>
+      <c r="P113" s="9">
+        <v>237.4</v>
+      </c>
+      <c r="Q113" s="10">
+        <v>5.91</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>41456</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F114" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H114" s="9">
+        <v>30.21</v>
+      </c>
+      <c r="I114" s="10">
+        <v>3.44</v>
+      </c>
+      <c r="J114" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="K114" s="9">
+        <v>206.6</v>
+      </c>
+      <c r="L114" s="10">
+        <v>5.48</v>
+      </c>
+      <c r="M114" s="9">
+        <v>30.21</v>
+      </c>
+      <c r="N114" s="10">
+        <v>3.45</v>
+      </c>
+      <c r="O114" s="10">
+        <v>1.6</v>
+      </c>
+      <c r="P114" s="9">
+        <v>206.6</v>
+      </c>
+      <c r="Q114" s="10">
+        <v>5.48</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>41426</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H115" s="9">
+        <v>29.21</v>
+      </c>
+      <c r="I115" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="J115" s="10">
+        <v>10.7</v>
+      </c>
+      <c r="K115" s="9">
+        <v>176.4</v>
+      </c>
+      <c r="L115" s="10">
+        <v>6.17</v>
+      </c>
+      <c r="M115" s="9">
+        <v>29.21</v>
+      </c>
+      <c r="N115" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="O115" s="10">
+        <v>10.7</v>
+      </c>
+      <c r="P115" s="9">
+        <v>176.4</v>
+      </c>
+      <c r="Q115" s="10">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>41395</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H116" s="9">
+        <v>29.19</v>
+      </c>
+      <c r="I116" s="8">
+        <v>-1.54</v>
+      </c>
+      <c r="J116" s="10">
+        <v>6.69</v>
+      </c>
+      <c r="K116" s="9">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="L116" s="10">
+        <v>5.31</v>
+      </c>
+      <c r="M116" s="9">
+        <v>29.19</v>
+      </c>
+      <c r="N116" s="8">
+        <v>-1.54</v>
+      </c>
+      <c r="O116" s="10">
+        <v>6.7</v>
+      </c>
+      <c r="P116" s="9">
+        <v>147.19999999999999</v>
+      </c>
+      <c r="Q116" s="10">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>41365</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H117" s="9">
+        <v>29.65</v>
+      </c>
+      <c r="I117" s="8">
+        <v>-2.94</v>
+      </c>
+      <c r="J117" s="10">
+        <v>9.01</v>
+      </c>
+      <c r="K117" s="9">
+        <v>118</v>
+      </c>
+      <c r="L117" s="10">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="M117" s="9">
+        <v>29.65</v>
+      </c>
+      <c r="N117" s="8">
+        <v>-2.95</v>
+      </c>
+      <c r="O117" s="10">
+        <v>9.01</v>
+      </c>
+      <c r="P117" s="9">
+        <v>118</v>
+      </c>
+      <c r="Q117" s="10">
+        <v>4.9800000000000004</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>41334</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H118" s="9">
+        <v>30.55</v>
+      </c>
+      <c r="I118" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="J118" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="K118" s="9">
+        <v>88.39</v>
+      </c>
+      <c r="L118" s="10">
+        <v>3.69</v>
+      </c>
+      <c r="M118" s="9">
+        <v>30.55</v>
+      </c>
+      <c r="N118" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="O118" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="P118" s="9">
+        <v>88.39</v>
+      </c>
+      <c r="Q118" s="10">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>41306</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H119" s="9">
+        <v>30.5</v>
+      </c>
+      <c r="I119" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="J119" s="10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="K119" s="9">
+        <v>57.84</v>
+      </c>
+      <c r="L119" s="9">
+        <v>0</v>
+      </c>
+      <c r="M119" s="9">
+        <v>30.5</v>
+      </c>
+      <c r="N119" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="O119" s="10">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="P119" s="9">
+        <v>57.84</v>
+      </c>
+      <c r="Q119" s="10">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>41275</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H120" s="9">
+        <v>27.35</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="8">
+        <v>-13.8</v>
+      </c>
+      <c r="K120" s="9">
+        <v>27.35</v>
+      </c>
+      <c r="L120" s="8">
+        <v>-13.8</v>
+      </c>
+      <c r="M120" s="9">
+        <v>27.35</v>
+      </c>
+      <c r="N120" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O120" s="8">
+        <v>-13.9</v>
+      </c>
+      <c r="P120" s="9">
+        <v>27.35</v>
+      </c>
+      <c r="Q120" s="8">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>41244</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H121" s="9">
+        <v>30.4</v>
+      </c>
+      <c r="I121" s="10">
+        <v>7.27</v>
+      </c>
+      <c r="J121" s="10">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="K121" s="9">
+        <v>339.8</v>
+      </c>
+      <c r="L121" s="10">
+        <v>5.42</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P121" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q121" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>41214</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H122" s="9">
+        <v>28.33</v>
+      </c>
+      <c r="I122" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="J122" s="10">
+        <v>6.01</v>
+      </c>
+      <c r="K122" s="9">
+        <v>309.39999999999998</v>
+      </c>
+      <c r="L122" s="10">
+        <v>4.97</v>
+      </c>
+      <c r="M122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P122" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q122" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>41183</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H123" s="9">
+        <v>28.86</v>
+      </c>
+      <c r="I123" s="10">
+        <v>2.74</v>
+      </c>
+      <c r="J123" s="10">
+        <v>2.04</v>
+      </c>
+      <c r="K123" s="9">
+        <v>281.10000000000002</v>
+      </c>
+      <c r="L123" s="10">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="M123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P123" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q123" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>41153</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H124" s="9">
+        <v>28.08</v>
+      </c>
+      <c r="I124" s="8">
+        <v>-0.41</v>
+      </c>
+      <c r="J124" s="10">
+        <v>5.37</v>
+      </c>
+      <c r="K124" s="9">
+        <v>252.3</v>
+      </c>
+      <c r="L124" s="10">
+        <v>5.2</v>
+      </c>
+      <c r="M124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P124" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q124" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>41122</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H125" s="9">
+        <v>28.2</v>
+      </c>
+      <c r="I125" s="8">
+        <v>-5.13</v>
+      </c>
+      <c r="J125" s="10">
+        <v>5.33</v>
+      </c>
+      <c r="K125" s="9">
+        <v>224.2</v>
+      </c>
+      <c r="L125" s="10">
+        <v>5.18</v>
+      </c>
+      <c r="M125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P125" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q125" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>41091</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H126" s="9">
+        <v>29.73</v>
+      </c>
+      <c r="I126" s="10">
+        <v>12.6</v>
+      </c>
+      <c r="J126" s="10">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="K126" s="9">
+        <v>196</v>
+      </c>
+      <c r="L126" s="10">
+        <v>5.15</v>
+      </c>
+      <c r="M126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P126" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q126" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>41061</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H127" s="9">
+        <v>26.39</v>
+      </c>
+      <c r="I127" s="8">
+        <v>-3.51</v>
+      </c>
+      <c r="J127" s="8">
+        <v>-0.09</v>
+      </c>
+      <c r="K127" s="9">
+        <v>166.2</v>
+      </c>
+      <c r="L127" s="10">
+        <v>5.22</v>
+      </c>
+      <c r="M127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P127" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q127" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>41030</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H128" s="9">
+        <v>27.36</v>
+      </c>
+      <c r="I128" s="10">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="J128" s="10">
+        <v>6.25</v>
+      </c>
+      <c r="K128" s="9">
+        <v>139.80000000000001</v>
+      </c>
+      <c r="L128" s="10">
+        <v>6.29</v>
+      </c>
+      <c r="M128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P128" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q128" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>41000</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H129" s="9">
+        <v>27.2</v>
+      </c>
+      <c r="I129" s="8">
+        <v>-0.95</v>
+      </c>
+      <c r="J129" s="8">
+        <v>-0.12</v>
+      </c>
+      <c r="K129" s="9">
+        <v>112.5</v>
+      </c>
+      <c r="L129" s="10">
+        <v>6.31</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P129" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q129" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>40969</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H130" s="9">
+        <v>27.46</v>
+      </c>
+      <c r="I130" s="10">
+        <v>5.22</v>
+      </c>
+      <c r="J130" s="10">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="K130" s="9">
+        <v>85.3</v>
+      </c>
+      <c r="L130" s="10">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="M130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P130" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q130" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>40940</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H131" s="9">
+        <v>26.09</v>
+      </c>
+      <c r="I131" s="8">
+        <v>-17.8</v>
+      </c>
+      <c r="J131" s="8">
+        <v>-7.7</v>
+      </c>
+      <c r="K131" s="9">
+        <v>57.84</v>
+      </c>
+      <c r="L131" s="10">
+        <v>8.58</v>
+      </c>
+      <c r="M131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P131" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q131" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>40909</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H132" s="9">
+        <v>31.75</v>
+      </c>
+      <c r="I132" s="10">
+        <v>15.1</v>
+      </c>
+      <c r="J132" s="10">
+        <v>27</v>
+      </c>
+      <c r="K132" s="9">
+        <v>31.75</v>
+      </c>
+      <c r="L132" s="10">
+        <v>27</v>
+      </c>
+      <c r="M132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P132" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q132" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>40878</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H133" s="9">
+        <v>27.58</v>
+      </c>
+      <c r="I133" s="10">
+        <v>3.18</v>
+      </c>
+      <c r="J133" s="10">
+        <v>6.02</v>
+      </c>
+      <c r="K133" s="9">
+        <v>322.39999999999998</v>
+      </c>
+      <c r="L133" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P133" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q133" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>40848</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H134" s="9">
+        <v>26.73</v>
+      </c>
+      <c r="I134" s="8">
+        <v>-5.48</v>
+      </c>
+      <c r="J134" s="10">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="K134" s="9">
+        <v>294.8</v>
+      </c>
+      <c r="L134" s="10">
+        <v>17.8</v>
+      </c>
+      <c r="M134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P134" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q134" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>40817</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H135" s="9">
+        <v>28.28</v>
+      </c>
+      <c r="I135" s="10">
+        <v>6.09</v>
+      </c>
+      <c r="J135" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="K135" s="9">
+        <v>268.10000000000002</v>
+      </c>
+      <c r="L135" s="10">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="M135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P135" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q135" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>40787</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H136" s="9">
+        <v>26.65</v>
+      </c>
+      <c r="I136" s="8">
+        <v>-0.44</v>
+      </c>
+      <c r="J136" s="10">
+        <v>20</v>
+      </c>
+      <c r="K136" s="9">
+        <v>239.8</v>
+      </c>
+      <c r="L136" s="10">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P136" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q136" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>40756</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H137" s="9">
+        <v>26.77</v>
+      </c>
+      <c r="I137" s="8">
+        <v>-5.64</v>
+      </c>
+      <c r="J137" s="10">
+        <v>7.43</v>
+      </c>
+      <c r="K137" s="9">
+        <v>213.1</v>
+      </c>
+      <c r="L137" s="10">
+        <v>18.7</v>
+      </c>
+      <c r="M137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P137" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q137" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>40725</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H138" s="9">
+        <v>28.37</v>
+      </c>
+      <c r="I138" s="10">
+        <v>7.39</v>
+      </c>
+      <c r="J138" s="10">
+        <v>14.6</v>
+      </c>
+      <c r="K138" s="9">
+        <v>186.4</v>
+      </c>
+      <c r="L138" s="10">
+        <v>20.6</v>
+      </c>
+      <c r="M138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P138" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q138" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>40695</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H139" s="9">
+        <v>26.42</v>
+      </c>
+      <c r="I139" s="10">
+        <v>2.61</v>
+      </c>
+      <c r="J139" s="10">
+        <v>24.8</v>
+      </c>
+      <c r="K139" s="9">
+        <v>158</v>
+      </c>
+      <c r="L139" s="10">
+        <v>21.7</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P139" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q139" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>40664</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H140" s="9">
+        <v>25.75</v>
+      </c>
+      <c r="I140" s="8">
+        <v>-5.44</v>
+      </c>
+      <c r="J140" s="10">
+        <v>14.7</v>
+      </c>
+      <c r="K140" s="9">
+        <v>131.6</v>
+      </c>
+      <c r="L140" s="10">
+        <v>21.1</v>
+      </c>
+      <c r="M140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P140" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q140" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>40634</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H141" s="9">
+        <v>27.23</v>
+      </c>
+      <c r="I141" s="10">
+        <v>7.55</v>
+      </c>
+      <c r="J141" s="10">
+        <v>23</v>
+      </c>
+      <c r="K141" s="9">
+        <v>105.8</v>
+      </c>
+      <c r="L141" s="10">
+        <v>22.8</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P141" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q141" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>40603</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H142" s="9">
+        <v>25.32</v>
+      </c>
+      <c r="I142" s="8">
+        <v>-10.4</v>
+      </c>
+      <c r="J142" s="10">
+        <v>25.6</v>
+      </c>
+      <c r="K142" s="9">
+        <v>78.59</v>
+      </c>
+      <c r="L142" s="10">
+        <v>22.7</v>
+      </c>
+      <c r="M142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P142" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q142" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>40575</v>
+      </c>
+      <c r="B143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H143" s="9">
+        <v>28.27</v>
+      </c>
+      <c r="I143" s="10">
+        <v>13.1</v>
+      </c>
+      <c r="J143" s="10">
+        <v>21.4</v>
+      </c>
+      <c r="K143" s="9">
+        <v>53.27</v>
+      </c>
+      <c r="L143" s="10">
+        <v>21.4</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P143" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q143" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>40544</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H144" s="9">
+        <v>25</v>
+      </c>
+      <c r="I144" s="8">
+        <v>-3.9</v>
+      </c>
+      <c r="J144" s="10">
+        <v>21.3</v>
+      </c>
+      <c r="K144" s="9">
+        <v>25</v>
+      </c>
+      <c r="L144" s="10">
+        <v>21.3</v>
+      </c>
+      <c r="M144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P144" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q144" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>40513</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H145" s="9">
+        <v>26.01</v>
+      </c>
+      <c r="I145" s="10">
+        <v>6.93</v>
+      </c>
+      <c r="J145" s="10">
+        <v>23.2</v>
+      </c>
+      <c r="K145" s="9">
+        <v>276.39999999999998</v>
+      </c>
+      <c r="L145" s="10">
+        <v>18.5</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P145" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q145" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>40483</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H146" s="9">
+        <v>24.32</v>
+      </c>
+      <c r="I146" s="8">
+        <v>-0.01</v>
+      </c>
+      <c r="J146" s="10">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="K146" s="9">
+        <v>250.3</v>
+      </c>
+      <c r="L146" s="10">
+        <v>18</v>
+      </c>
+      <c r="M146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P146" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q146" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>40452</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H147" s="9">
+        <v>24.33</v>
+      </c>
+      <c r="I147" s="10">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="J147" s="10">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="K147" s="9">
+        <v>226</v>
+      </c>
+      <c r="L147" s="10">
+        <v>17.8</v>
+      </c>
+      <c r="M147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P147" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q147" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>40422</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H148" s="9">
+        <v>22.21</v>
+      </c>
+      <c r="I148" s="8">
+        <v>-10.9</v>
+      </c>
+      <c r="J148" s="10">
+        <v>29.2</v>
+      </c>
+      <c r="K148" s="9">
+        <v>201.7</v>
+      </c>
+      <c r="L148" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="M148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P148" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q148" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>40391</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H149" s="9">
+        <v>24.92</v>
+      </c>
+      <c r="I149" s="10">
+        <v>0.62</v>
+      </c>
+      <c r="J149" s="10">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="K149" s="9">
+        <v>179.5</v>
+      </c>
+      <c r="L149" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="M149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P149" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q149" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>40360</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H150" s="9">
+        <v>24.77</v>
+      </c>
+      <c r="I150" s="10">
+        <v>17</v>
+      </c>
+      <c r="J150" s="10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="K150" s="9">
+        <v>154.6</v>
+      </c>
+      <c r="L150" s="10">
+        <v>13.7</v>
+      </c>
+      <c r="M150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P150" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q150" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>40330</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H151" s="9">
+        <v>21.17</v>
+      </c>
+      <c r="I151" s="8">
+        <v>-5.71</v>
+      </c>
+      <c r="J151" s="10">
+        <v>21.9</v>
+      </c>
+      <c r="K151" s="9">
+        <v>129.80000000000001</v>
+      </c>
+      <c r="L151" s="10">
+        <v>12.8</v>
+      </c>
+      <c r="M151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P151" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q151" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>40299</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H152" s="9">
+        <v>22.45</v>
+      </c>
+      <c r="I152" s="10">
+        <v>1.42</v>
+      </c>
+      <c r="J152" s="10">
+        <v>10</v>
+      </c>
+      <c r="K152" s="9">
+        <v>108.6</v>
+      </c>
+      <c r="L152" s="10">
+        <v>11.2</v>
+      </c>
+      <c r="M152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P152" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q152" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A153" s="6">
+        <v>40269</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H153" s="9">
+        <v>22.14</v>
+      </c>
+      <c r="I153" s="10">
+        <v>9.84</v>
+      </c>
+      <c r="J153" s="10">
+        <v>19.3</v>
+      </c>
+      <c r="K153" s="9">
+        <v>86.18</v>
+      </c>
+      <c r="L153" s="10">
+        <v>11.5</v>
+      </c>
+      <c r="M153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P153" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q153" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A154" s="6">
+        <v>40238</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H154" s="9">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="I154" s="8">
+        <v>-13.4</v>
+      </c>
+      <c r="J154" s="10">
+        <v>5.58</v>
+      </c>
+      <c r="K154" s="9">
+        <v>64.040000000000006</v>
+      </c>
+      <c r="L154" s="10">
+        <v>9</v>
+      </c>
+      <c r="M154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P154" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q154" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A155" s="6">
+        <v>40210</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H155" s="9">
+        <v>23.28</v>
+      </c>
+      <c r="I155" s="10">
+        <v>13</v>
+      </c>
+      <c r="J155" s="10">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="K155" s="9">
+        <v>43.89</v>
+      </c>
+      <c r="L155" s="10">
+        <v>10.6</v>
+      </c>
+      <c r="M155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P155" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q155" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A156" s="6">
+        <v>40179</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H156" s="9">
+        <v>20.6</v>
+      </c>
+      <c r="I156" s="8">
+        <v>-2.37</v>
+      </c>
+      <c r="J156" s="8">
+        <v>-7.64</v>
+      </c>
+      <c r="K156" s="9">
+        <v>20.6</v>
+      </c>
+      <c r="L156" s="8">
+        <v>-7.64</v>
+      </c>
+      <c r="M156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P156" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q156" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A157" s="6">
+        <v>40148</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H157" s="9">
+        <v>21.11</v>
+      </c>
+      <c r="I157" s="10">
+        <v>4.01</v>
+      </c>
+      <c r="J157" s="10">
+        <v>5.97</v>
+      </c>
+      <c r="K157" s="9">
+        <v>233.2</v>
+      </c>
+      <c r="L157" s="10">
+        <v>1.19</v>
+      </c>
+      <c r="M157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P157" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q157" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A158" s="6">
+        <v>40118</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H158" s="9">
+        <v>20.29</v>
+      </c>
+      <c r="I158" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="J158" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="K158" s="9">
+        <v>212.1</v>
+      </c>
+      <c r="L158" s="10">
+        <v>0.74</v>
+      </c>
+      <c r="M158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P158" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q158" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A159" s="6">
+        <v>40087</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H159" s="9">
+        <v>20.25</v>
+      </c>
+      <c r="I159" s="10">
+        <v>17.8</v>
+      </c>
+      <c r="J159" s="8">
+        <v>-4.0199999999999996</v>
+      </c>
+      <c r="K159" s="9">
+        <v>191.8</v>
+      </c>
+      <c r="L159" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="M159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P159" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q159" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A160" s="6">
+        <v>40057</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H160" s="9">
+        <v>17.18</v>
+      </c>
+      <c r="I160" s="8">
+        <v>-6.71</v>
+      </c>
+      <c r="J160" s="8">
+        <v>-5.39</v>
+      </c>
+      <c r="K160" s="9">
+        <v>171.6</v>
+      </c>
+      <c r="L160" s="10">
+        <v>1.42</v>
+      </c>
+      <c r="M160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P160" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q160" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A161" s="6">
+        <v>40026</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H161" s="9">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="I161" s="8">
+        <v>-11.9</v>
+      </c>
+      <c r="J161" s="8">
+        <v>-15.1</v>
+      </c>
+      <c r="K161" s="9">
+        <v>154.4</v>
+      </c>
+      <c r="L161" s="10">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="M161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P161" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q161" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A162" s="6">
+        <v>39995</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H162" s="9">
+        <v>20.91</v>
+      </c>
+      <c r="I162" s="10">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="J162" s="10">
+        <v>2.59</v>
+      </c>
+      <c r="K162" s="9">
+        <v>136</v>
+      </c>
+      <c r="L162" s="10">
+        <v>5.15</v>
+      </c>
+      <c r="M162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P162" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q162" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A163" s="6">
+        <v>39965</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H163" s="9">
+        <v>17.37</v>
+      </c>
+      <c r="I163" s="8">
+        <v>-14.9</v>
+      </c>
+      <c r="J163" s="8">
+        <v>-7.42</v>
+      </c>
+      <c r="K163" s="9">
+        <v>115.1</v>
+      </c>
+      <c r="L163" s="10">
+        <v>5.63</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q163" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A164" s="6">
+        <v>39934</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H164" s="9">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="I164" s="10">
+        <v>9.92</v>
+      </c>
+      <c r="J164" s="10">
+        <v>5.44</v>
+      </c>
+      <c r="K164" s="9">
+        <v>97.71</v>
+      </c>
+      <c r="L164" s="10">
+        <v>8.34</v>
+      </c>
+      <c r="M164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P164" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q164" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A165" s="6">
+        <v>39904</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H165" s="9">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="I165" s="8">
+        <v>-2.76</v>
+      </c>
+      <c r="J165" s="8">
+        <v>-2.31</v>
+      </c>
+      <c r="K165" s="9">
+        <v>77.31</v>
+      </c>
+      <c r="L165" s="10">
+        <v>9.1300000000000008</v>
+      </c>
+      <c r="M165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P165" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q165" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A166" s="6">
+        <v>39873</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H166" s="9">
+        <v>19.09</v>
+      </c>
+      <c r="I166" s="10">
+        <v>10</v>
+      </c>
+      <c r="J166" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="K166" s="9">
+        <v>58.75</v>
+      </c>
+      <c r="L166" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="M166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P166" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q166" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A167" s="6">
+        <v>39845</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H167" s="9">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="I167" s="8">
+        <v>-22.2</v>
+      </c>
+      <c r="J167" s="10">
+        <v>0.37</v>
+      </c>
+      <c r="K167" s="9">
+        <v>39.659999999999997</v>
+      </c>
+      <c r="L167" s="10">
+        <v>20.9</v>
+      </c>
+      <c r="M167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P167" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q167" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A168" s="6">
+        <v>39814</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H168" s="9">
+        <v>22.31</v>
+      </c>
+      <c r="I168" s="10">
+        <v>12</v>
+      </c>
+      <c r="J168" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="K168" s="9">
+        <v>22.31</v>
+      </c>
+      <c r="L168" s="10">
+        <v>43.8</v>
+      </c>
+      <c r="M168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P168" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q168" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A169" s="6">
+        <v>39783</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H169" s="9">
+        <v>19.920000000000002</v>
+      </c>
+      <c r="I169" s="8">
+        <v>-1.83</v>
+      </c>
+      <c r="J169" s="10">
+        <v>26.2</v>
+      </c>
+      <c r="K169" s="9">
+        <v>230.5</v>
+      </c>
+      <c r="L169" s="10">
+        <v>70.7</v>
+      </c>
+      <c r="M169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P169" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q169" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>39753</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H170" s="9">
+        <v>20.29</v>
+      </c>
+      <c r="I170" s="8">
+        <v>-3.84</v>
+      </c>
+      <c r="J170" s="10">
+        <v>43.5</v>
+      </c>
+      <c r="K170" s="9">
+        <v>210.6</v>
+      </c>
+      <c r="L170" s="10">
+        <v>76.599999999999994</v>
+      </c>
+      <c r="M170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P170" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q170" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A171" s="6">
+        <v>39722</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H171" s="9">
+        <v>21.1</v>
+      </c>
+      <c r="I171" s="10">
+        <v>16.2</v>
+      </c>
+      <c r="J171" s="10">
+        <v>59.8</v>
+      </c>
+      <c r="K171" s="9">
+        <v>190.3</v>
+      </c>
+      <c r="L171" s="10">
+        <v>81</v>
+      </c>
+      <c r="M171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P171" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q171" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A172" s="6">
+        <v>39692</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H172" s="9">
+        <v>18.16</v>
+      </c>
+      <c r="I172" s="8">
+        <v>-16.2</v>
+      </c>
+      <c r="J172" s="10">
+        <v>43.2</v>
+      </c>
+      <c r="K172" s="9">
+        <v>169.2</v>
+      </c>
+      <c r="L172" s="10">
+        <v>84.1</v>
+      </c>
+      <c r="M172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P172" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q172" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A173" s="6">
+        <v>39661</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H173" s="9">
+        <v>21.69</v>
+      </c>
+      <c r="I173" s="10">
+        <v>6.38</v>
+      </c>
+      <c r="J173" s="10">
+        <v>72.2</v>
+      </c>
+      <c r="K173" s="9">
+        <v>151</v>
+      </c>
+      <c r="L173" s="10">
+        <v>90.6</v>
+      </c>
+      <c r="M173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P173" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q173" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A174" s="6">
+        <v>39630</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H174" s="9">
+        <v>20.38</v>
+      </c>
+      <c r="I174" s="10">
+        <v>8.65</v>
+      </c>
+      <c r="J174" s="10">
+        <v>59</v>
+      </c>
+      <c r="K174" s="9">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="L174" s="10">
+        <v>94.1</v>
+      </c>
+      <c r="M174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P174" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q174" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A175" s="6">
+        <v>39600</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H175" s="9">
+        <v>18.760000000000002</v>
+      </c>
+      <c r="I175" s="8">
+        <v>-3.05</v>
+      </c>
+      <c r="J175" s="10">
+        <v>65.099999999999994</v>
+      </c>
+      <c r="K175" s="9">
+        <v>108.9</v>
+      </c>
+      <c r="L175" s="10">
+        <v>102.5</v>
+      </c>
+      <c r="M175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P175" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q175" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A176" s="6">
+        <v>39569</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H176" s="9">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="I176" s="10">
+        <v>1.84</v>
+      </c>
+      <c r="J176" s="10">
+        <v>79.5</v>
+      </c>
+      <c r="K176" s="9">
+        <v>90.18</v>
+      </c>
+      <c r="L176" s="10">
+        <v>112.5</v>
+      </c>
+      <c r="M176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P176" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q176" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A177" s="6">
+        <v>39539</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H177" s="9">
+        <v>19</v>
+      </c>
+      <c r="I177" s="8">
+        <v>-0.2</v>
+      </c>
+      <c r="J177" s="10">
+        <v>84.4</v>
+      </c>
+      <c r="K177" s="9">
+        <v>70.83</v>
+      </c>
+      <c r="L177" s="10">
+        <v>123.7</v>
+      </c>
+      <c r="M177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P177" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q177" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A178" s="6">
+        <v>39508</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H178" s="9">
+        <v>19.04</v>
+      </c>
+      <c r="I178" s="10">
+        <v>10.1</v>
+      </c>
+      <c r="J178" s="10">
+        <v>119.4</v>
+      </c>
+      <c r="K178" s="9">
+        <v>51.83</v>
+      </c>
+      <c r="L178" s="10">
+        <v>142.6</v>
+      </c>
+      <c r="M178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q178" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A179" s="6">
+        <v>39479</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H179" s="9">
+        <v>17.29</v>
+      </c>
+      <c r="I179" s="10">
+        <v>11.4</v>
+      </c>
+      <c r="J179" s="10">
+        <v>158.30000000000001</v>
+      </c>
+      <c r="K179" s="9">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="L179" s="10">
+        <v>158.5</v>
+      </c>
+      <c r="M179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P179" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q179" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A180" s="6">
+        <v>39448</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H180" s="9">
+        <v>15.51</v>
+      </c>
+      <c r="I180" s="8">
+        <v>-1.73</v>
+      </c>
+      <c r="J180" s="10">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="K180" s="9">
+        <v>15.51</v>
+      </c>
+      <c r="L180" s="10">
+        <v>158.80000000000001</v>
+      </c>
+      <c r="M180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P180" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q180" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A181" s="6">
+        <v>39417</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H181" s="9">
+        <v>15.78</v>
+      </c>
+      <c r="I181" s="10">
+        <v>11.6</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K181" s="9">
+        <v>135</v>
+      </c>
+      <c r="L181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P181" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q181" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A182" s="6">
+        <v>39387</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H182" s="9">
+        <v>14.14</v>
+      </c>
+      <c r="I182" s="10">
+        <v>7.08</v>
+      </c>
+      <c r="J182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K182" s="9">
+        <v>119.2</v>
+      </c>
+      <c r="L182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P182" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q182" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A183" s="6">
+        <v>39356</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H183" s="9">
+        <v>13.2</v>
+      </c>
+      <c r="I183" s="10">
+        <v>4.1100000000000003</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K183" s="9">
+        <v>105.1</v>
+      </c>
+      <c r="L183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q183" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A184" s="6">
+        <v>39326</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H184" s="9">
+        <v>12.68</v>
+      </c>
+      <c r="I184" s="10">
+        <v>0.73</v>
+      </c>
+      <c r="J184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K184" s="9">
+        <v>91.9</v>
+      </c>
+      <c r="L184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P184" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q184" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A185" s="6">
+        <v>39295</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H185" s="9">
+        <v>12.59</v>
+      </c>
+      <c r="I185" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="J185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K185" s="9">
+        <v>79.22</v>
+      </c>
+      <c r="L185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P185" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q185" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A186" s="6">
+        <v>39264</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H186" s="9">
+        <v>12.82</v>
+      </c>
+      <c r="I186" s="10">
+        <v>12.9</v>
+      </c>
+      <c r="J186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K186" s="9">
+        <v>66.63</v>
+      </c>
+      <c r="L186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P186" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q186" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A187" s="6">
+        <v>39234</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H187" s="9">
+        <v>11.36</v>
+      </c>
+      <c r="I187" s="10">
+        <v>5.35</v>
+      </c>
+      <c r="J187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K187" s="9">
+        <v>53.81</v>
+      </c>
+      <c r="L187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P187" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q187" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A188" s="6">
+        <v>39203</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H188" s="9">
+        <v>10.78</v>
+      </c>
+      <c r="I188" s="10">
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="J188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K188" s="9">
+        <v>42.45</v>
+      </c>
+      <c r="L188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P188" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q188" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A189" s="6">
+        <v>39173</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H189" s="9">
+        <v>10.3</v>
+      </c>
+      <c r="I189" s="10">
+        <v>18.7</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K189" s="9">
+        <v>31.66</v>
+      </c>
+      <c r="L189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P189" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q189" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A190" s="6">
+        <v>39142</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H190" s="9">
+        <v>8.68</v>
+      </c>
+      <c r="I190" s="10">
+        <v>29.6</v>
+      </c>
+      <c r="J190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K190" s="9">
+        <v>21.36</v>
+      </c>
+      <c r="L190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P190" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q190" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>39114</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H191" s="9">
+        <v>6.69</v>
+      </c>
+      <c r="I191" s="10">
+        <v>11.7</v>
+      </c>
+      <c r="J191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K191" s="9">
+        <v>12.69</v>
+      </c>
+      <c r="L191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P191" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q191" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A192" s="6">
+        <v>39083</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H192" s="9">
+        <v>5.99</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K192" s="9">
+        <v>5.99</v>
+      </c>
+      <c r="L192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P192" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q192" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A193" s="6">
+        <v>39052</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H193" s="9">
+        <v>0</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K193" s="9">
+        <v>0</v>
+      </c>
+      <c r="L193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P193" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q193" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>39022</v>
+      </c>
+      <c r="B194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H194" s="9">
+        <v>0</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K194" s="9">
+        <v>0</v>
+      </c>
+      <c r="L194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P194" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q194" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A195" s="6">
+        <v>38991</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E195" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H195" s="9">
+        <v>0</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K195" s="9">
+        <v>0</v>
+      </c>
+      <c r="L195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P195" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q195" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A196" s="6">
+        <v>38961</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H196" s="9">
+        <v>0</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K196" s="9">
+        <v>0</v>
+      </c>
+      <c r="L196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P196" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q196" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A197" s="6">
+        <v>38930</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H197" s="9">
+        <v>0</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K197" s="9">
+        <v>0</v>
+      </c>
+      <c r="L197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P197" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q197" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A198" s="6">
+        <v>38899</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H198" s="9">
+        <v>0</v>
+      </c>
+      <c r="I198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K198" s="9">
+        <v>0</v>
+      </c>
+      <c r="L198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P198" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q198" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A199" s="6">
+        <v>38869</v>
+      </c>
+      <c r="B199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H199" s="9">
+        <v>0</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K199" s="9">
+        <v>0</v>
+      </c>
+      <c r="L199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q199" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A200" s="6">
+        <v>38838</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H200" s="9">
+        <v>0</v>
+      </c>
+      <c r="I200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K200" s="9">
+        <v>0</v>
+      </c>
+      <c r="L200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P200" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q200" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A201" s="6">
+        <v>38808</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H201" s="9">
+        <v>0</v>
+      </c>
+      <c r="I201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K201" s="9">
+        <v>0</v>
+      </c>
+      <c r="L201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P201" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q201" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A202" s="6">
+        <v>38777</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H202" s="9">
+        <v>0</v>
+      </c>
+      <c r="I202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K202" s="9">
+        <v>0</v>
+      </c>
+      <c r="L202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P202" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q202" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A203" s="6">
+        <v>38749</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H203" s="9">
+        <v>0</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K203" s="9">
+        <v>0</v>
+      </c>
+      <c r="L203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P203" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q203" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A204" s="6">
+        <v>38718</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H204" s="9">
+        <v>0</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K204" s="9">
+        <v>0</v>
+      </c>
+      <c r="L204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P204" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q204" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A205" s="6">
+        <v>38687</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H205" s="9">
+        <v>0</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K205" s="9">
+        <v>0</v>
+      </c>
+      <c r="L205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P205" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q205" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A206" s="6">
+        <v>38657</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H206" s="9">
+        <v>0</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K206" s="9">
+        <v>0</v>
+      </c>
+      <c r="L206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P206" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q206" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A207" s="6">
+        <v>38626</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H207" s="9">
+        <v>0</v>
+      </c>
+      <c r="I207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K207" s="9">
+        <v>0</v>
+      </c>
+      <c r="L207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P207" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q207" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A208" s="6">
+        <v>38596</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H208" s="9">
+        <v>0</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K208" s="9">
+        <v>0</v>
+      </c>
+      <c r="L208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P208" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q208" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A209" s="6">
+        <v>38565</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H209" s="9">
+        <v>0</v>
+      </c>
+      <c r="I209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K209" s="9">
+        <v>0</v>
+      </c>
+      <c r="L209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P209" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q209" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A210" s="6">
+        <v>38534</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H210" s="9">
+        <v>0</v>
+      </c>
+      <c r="I210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K210" s="9">
+        <v>0</v>
+      </c>
+      <c r="L210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P210" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q210" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A211" s="6">
+        <v>38504</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H211" s="9">
+        <v>0</v>
+      </c>
+      <c r="I211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K211" s="9">
+        <v>0</v>
+      </c>
+      <c r="L211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P211" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q211" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A212" s="6">
+        <v>38473</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H212" s="9">
+        <v>0</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K212" s="9">
+        <v>0</v>
+      </c>
+      <c r="L212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P212" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q212" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A213" s="6">
+        <v>38443</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H213" s="9">
+        <v>0</v>
+      </c>
+      <c r="I213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K213" s="9">
+        <v>0</v>
+      </c>
+      <c r="L213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P213" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q213" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A214" s="6">
+        <v>38412</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H214" s="9">
+        <v>0</v>
+      </c>
+      <c r="I214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K214" s="9">
+        <v>0</v>
+      </c>
+      <c r="L214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P214" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q214" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A215" s="6">
+        <v>38384</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H215" s="9">
+        <v>0</v>
+      </c>
+      <c r="I215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K215" s="9">
+        <v>0</v>
+      </c>
+      <c r="L215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P215" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q215" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A216" s="6">
+        <v>38353</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H216" s="9">
+        <v>0</v>
+      </c>
+      <c r="I216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K216" s="9">
+        <v>0</v>
+      </c>
+      <c r="L216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P216" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q216" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A217" s="6">
+        <v>38322</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E217" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H217" s="9">
+        <v>0</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K217" s="9">
+        <v>0</v>
+      </c>
+      <c r="L217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P217" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q217" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A218" s="6">
+        <v>38292</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D218" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E218" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H218" s="9">
+        <v>0</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K218" s="9">
+        <v>0</v>
+      </c>
+      <c r="L218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P218" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q218" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A219" s="6">
+        <v>38261</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E219" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H219" s="9">
+        <v>0</v>
+      </c>
+      <c r="I219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K219" s="9">
+        <v>0</v>
+      </c>
+      <c r="L219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P219" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q219" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A220" s="6">
+        <v>38231</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D220" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E220" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H220" s="9">
+        <v>0</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K220" s="9">
+        <v>0</v>
+      </c>
+      <c r="L220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P220" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q220" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A221" s="6">
+        <v>38200</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H221" s="9">
+        <v>0</v>
+      </c>
+      <c r="I221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221" s="9">
+        <v>0</v>
+      </c>
+      <c r="L221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P221" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q221" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A222" s="6">
+        <v>38169</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H222" s="9">
+        <v>0</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K222" s="9">
+        <v>0</v>
+      </c>
+      <c r="L222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P222" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q222" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A223" s="6">
+        <v>38139</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E223" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H223" s="9">
+        <v>0</v>
+      </c>
+      <c r="I223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K223" s="9">
+        <v>0</v>
+      </c>
+      <c r="L223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P223" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q223" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A224" s="6">
+        <v>38108</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E224" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H224" s="9">
+        <v>0</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K224" s="9">
+        <v>0</v>
+      </c>
+      <c r="L224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P224" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q224" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A225" s="6">
+        <v>38078</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H225" s="9">
+        <v>0</v>
+      </c>
+      <c r="I225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K225" s="9">
+        <v>0</v>
+      </c>
+      <c r="L225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P225" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q225" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A226" s="6">
+        <v>38047</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H226" s="9">
+        <v>0</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K226" s="9">
+        <v>0</v>
+      </c>
+      <c r="L226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P226" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q226" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A227" s="6">
+        <v>38018</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E227" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H227" s="9">
+        <v>0</v>
+      </c>
+      <c r="I227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K227" s="9">
+        <v>0</v>
+      </c>
+      <c r="L227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P227" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q227" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A228" s="6">
+        <v>37987</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H228" s="9">
+        <v>0</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K228" s="9">
+        <v>0</v>
+      </c>
+      <c r="L228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P228" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q228" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A229" s="6">
+        <v>37956</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H229" s="9">
+        <v>0</v>
+      </c>
+      <c r="I229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K229" s="9">
+        <v>0</v>
+      </c>
+      <c r="L229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P229" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q229" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A230" s="6">
+        <v>37926</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H230" s="9">
+        <v>0</v>
+      </c>
+      <c r="I230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K230" s="9">
+        <v>0</v>
+      </c>
+      <c r="L230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P230" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q230" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A231" s="6">
+        <v>37895</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H231" s="9">
+        <v>0</v>
+      </c>
+      <c r="I231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K231" s="9">
+        <v>0</v>
+      </c>
+      <c r="L231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P231" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q231" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A232" s="6">
+        <v>37865</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H232" s="9">
+        <v>0</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K232" s="9">
+        <v>0</v>
+      </c>
+      <c r="L232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P232" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q232" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A233" s="6">
+        <v>37834</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H233" s="9">
+        <v>0</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K233" s="9">
+        <v>0</v>
+      </c>
+      <c r="L233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P233" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q233" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A234" s="6">
+        <v>37803</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H234" s="9">
+        <v>0</v>
+      </c>
+      <c r="I234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K234" s="9">
+        <v>0</v>
+      </c>
+      <c r="L234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P234" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q234" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A235" s="6">
+        <v>37773</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H235" s="9">
+        <v>0</v>
+      </c>
+      <c r="I235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K235" s="9">
+        <v>0</v>
+      </c>
+      <c r="L235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P235" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q235" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A236" s="6">
+        <v>37742</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H236" s="9">
+        <v>0</v>
+      </c>
+      <c r="I236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K236" s="9">
+        <v>0</v>
+      </c>
+      <c r="L236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P236" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q236" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A237" s="6">
+        <v>37712</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H237" s="9">
+        <v>0</v>
+      </c>
+      <c r="I237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K237" s="9">
+        <v>0</v>
+      </c>
+      <c r="L237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P237" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q237" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A238" s="6">
+        <v>37681</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E238" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H238" s="9">
+        <v>0</v>
+      </c>
+      <c r="I238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K238" s="9">
+        <v>0</v>
+      </c>
+      <c r="L238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P238" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q238" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A239" s="6">
+        <v>37653</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H239" s="9">
+        <v>0</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K239" s="9">
+        <v>0</v>
+      </c>
+      <c r="L239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P239" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q239" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A240" s="6">
+        <v>37622</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H240" s="9">
+        <v>0</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K240" s="9">
+        <v>0</v>
+      </c>
+      <c r="L240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P240" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q240" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4518,7 +13907,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>